--- a/results/Int BVP.xlsx
+++ b/results/Int BVP.xlsx
@@ -878,52 +878,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66.07 ± 5.92</t>
+          <t>65.58 ± 5.46</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.88 ± 5.44</t>
+          <t>66.38 ± 5.07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>66.23 ± 6.16</t>
+          <t>65.76 ± 5.66</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>72.70 ± 5.75</t>
+          <t>72.16 ± 5.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>76.28 ± 5.95</t>
+          <t>75.87 ± 5.94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.39 ± 11.83</t>
+          <t>31.42 ± 10.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>76.40 ± 5.72</t>
+          <t>75.96 ± 5.80</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>32.39 ± 4.90</t>
+          <t>32.68 ± 4.55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>37.24 ± 14.40</t>
+          <t>36.53 ± 13.50</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>26.56 ± 11.60</t>
+          <t>24.87 ± 10.46</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1310,52 +1310,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>65.58 ± 5.48</t>
+          <t>65.61 ± 5.13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.41 ± 4.90</t>
+          <t>66.42 ± 4.60</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>65.75 ± 5.67</t>
+          <t>65.79 ± 5.32</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>72.82 ± 5.51</t>
+          <t>72.38 ± 5.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>76.12 ± 5.95</t>
+          <t>75.74 ± 6.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.41 ± 10.87</t>
+          <t>31.47 ± 10.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>76.20 ± 5.78</t>
+          <t>75.79 ± 5.92</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>32.09 ± 4.05</t>
+          <t>32.57 ± 4.02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>37.33 ± 14.50</t>
+          <t>35.47 ± 13.66</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>25.81 ± 11.04</t>
+          <t>25.44 ± 12.68</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1742,52 +1742,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>65.22 ± 5.30</t>
+          <t>65.15 ± 5.85</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>66.09 ± 4.89</t>
+          <t>65.97 ± 5.43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>65.41 ± 5.58</t>
+          <t>65.33 ± 6.06</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>72.55 ± 5.69</t>
+          <t>72.09 ± 5.52</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>76.04 ± 5.83</t>
+          <t>75.66 ± 5.89</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.74 ± 10.64</t>
+          <t>30.54 ± 11.70</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>76.12 ± 5.70</t>
+          <t>75.73 ± 5.79</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.89 ± 4.47</t>
+          <t>33.16 ± 4.99</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>36.55 ± 13.52</t>
+          <t>37.19 ± 14.23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26.62 ± 12.77</t>
+          <t>26.04 ± 12.18</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2174,52 +2174,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>66.26 ± 5.23</t>
+          <t>65.42 ± 5.53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>67.06 ± 4.82</t>
+          <t>66.28 ± 4.98</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>66.47 ± 5.38</t>
+          <t>65.58 ± 5.88</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>72.44 ± 5.92</t>
+          <t>72.05 ± 5.64</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>75.97 ± 6.04</t>
+          <t>75.56 ± 6.41</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>32.80 ± 10.43</t>
+          <t>31.10 ± 11.09</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>76.06 ± 5.90</t>
+          <t>75.63 ± 6.28</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>32.36 ± 3.85</t>
+          <t>32.90 ± 4.25</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>37.21 ± 14.06</t>
+          <t>36.10 ± 15.17</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27.59 ± 12.62</t>
+          <t>25.48 ± 12.97</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2606,52 +2606,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>65.32 ± 6.13</t>
+          <t>65.50 ± 5.51</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>66.17 ± 5.72</t>
+          <t>66.33 ± 5.02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>65.51 ± 6.37</t>
+          <t>65.65 ± 5.80</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>72.32 ± 5.52</t>
+          <t>72.35 ± 6.03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>75.91 ± 5.76</t>
+          <t>75.63 ± 6.10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.91 ± 12.27</t>
+          <t>31.26 ± 11.01</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>75.99 ± 5.65</t>
+          <t>75.72 ± 5.92</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>32.72 ± 4.86</t>
+          <t>32.98 ± 4.25</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>36.62 ± 12.98</t>
+          <t>36.34 ± 13.81</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>25.47 ± 11.37</t>
+          <t>25.08 ± 11.51</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3038,52 +3038,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>67.33 ± 4.78</t>
+          <t>67.11 ± 4.51</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>67.87 ± 4.34</t>
+          <t>67.63 ± 4.04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67.37 ± 4.68</t>
+          <t>67.15 ± 4.29</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>74.30 ± 5.65</t>
+          <t>73.91 ± 5.65</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>77.53 ± 6.25</t>
+          <t>77.15 ± 6.40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>34.85 ± 9.40</t>
+          <t>34.39 ± 8.82</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>77.65 ± 5.97</t>
+          <t>77.30 ± 6.11</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30.78 ± 3.95</t>
+          <t>31.06 ± 3.89</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>39.75 ± 11.93</t>
+          <t>39.68 ± 13.06</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>28.25 ± 13.26</t>
+          <t>28.82 ± 13.91</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3470,52 +3470,52 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67.36 ± 6.23</t>
+          <t>67.36 ± 7.20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>67.74 ± 6.08</t>
+          <t>67.76 ± 6.98</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>67.41 ± 6.26</t>
+          <t>67.37 ± 7.31</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>74.00 ± 7.49</t>
+          <t>73.93 ± 7.25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>75.96 ± 8.99</t>
+          <t>75.57 ± 8.17</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>34.83 ± 12.42</t>
+          <t>34.84 ± 14.36</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>75.98 ± 8.95</t>
+          <t>75.61 ± 8.11</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>31.06 ± 6.35</t>
+          <t>31.21 ± 6.65</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>41.90 ± 18.59</t>
+          <t>40.48 ± 16.30</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>29.06 ± 17.13</t>
+          <t>27.59 ± 16.02</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3902,52 +3902,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>68.15 ± 6.80</t>
+          <t>67.90 ± 7.66</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>68.21 ± 6.79</t>
+          <t>67.97 ± 7.64</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67.97 ± 6.80</t>
+          <t>67.68 ± 7.72</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>73.56 ± 8.46</t>
+          <t>74.09 ± 9.27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>75.46 ± 8.13</t>
+          <t>75.95 ± 9.03</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>36.28 ± 13.56</t>
+          <t>35.78 ± 15.27</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>75.48 ± 8.18</t>
+          <t>75.96 ± 9.06</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>31.56 ± 6.85</t>
+          <t>31.19 ± 7.34</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>40.55 ± 17.09</t>
+          <t>43.23 ± 18.36</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>31.61 ± 14.91</t>
+          <t>31.69 ± 16.24</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4334,52 +4334,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>67.93 ± 7.70</t>
+          <t>67.65 ± 7.47</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>67.93 ± 7.65</t>
+          <t>67.64 ± 7.43</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>67.75 ± 7.59</t>
+          <t>67.45 ± 7.36</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>73.02 ± 9.44</t>
+          <t>72.66 ± 9.70</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>74.36 ± 10.04</t>
+          <t>73.96 ± 10.22</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>35.82 ± 15.35</t>
+          <t>35.24 ± 14.89</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>74.36 ± 10.03</t>
+          <t>73.95 ± 10.22</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>32.16 ± 7.99</t>
+          <t>31.88 ± 8.17</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>36.93 ± 18.17</t>
+          <t>37.04 ± 18.82</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>28.46 ± 16.71</t>
+          <t>28.21 ± 17.45</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4766,52 +4766,52 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>67.01 ± 5.20</t>
+          <t>67.18 ± 5.24</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>67.16 ± 5.24</t>
+          <t>67.34 ± 5.18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>66.82 ± 5.02</t>
+          <t>66.95 ± 5.08</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>72.69 ± 6.96</t>
+          <t>73.16 ± 6.51</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>71.26 ± 9.37</t>
+          <t>71.72 ± 8.95</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>34.02 ± 10.45</t>
+          <t>34.35 ± 10.46</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>71.35 ± 9.33</t>
+          <t>71.77 ± 8.95</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>32.88 ± 4.76</t>
+          <t>32.18 ± 5.13</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>35.84 ± 17.06</t>
+          <t>35.36 ± 15.26</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>25.58 ± 15.50</t>
+          <t>26.12 ± 14.21</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -5198,52 +5198,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>68.57 ± 6.01</t>
+          <t>67.12 ± 6.40</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>68.47 ± 5.99</t>
+          <t>67.03 ± 6.36</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>68.20 ± 6.14</t>
+          <t>66.67 ± 6.60</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>73.66 ± 8.07</t>
+          <t>73.28 ± 8.03</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>72.59 ± 8.37</t>
+          <t>72.09 ± 7.67</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>36.95 ± 11.97</t>
+          <t>34.07 ± 12.73</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>72.58 ± 8.37</t>
+          <t>72.11 ± 7.65</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>31.16 ± 6.84</t>
+          <t>31.76 ± 6.79</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>39.66 ± 12.97</t>
+          <t>40.02 ± 12.71</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>27.66 ± 12.41</t>
+          <t>27.21 ± 11.23</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5630,52 +5630,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>69.99 ± 8.02</t>
+          <t>70.18 ± 7.55</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.44 ± 8.14</t>
+          <t>70.65 ± 7.44</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>70.10 ± 8.22</t>
+          <t>70.31 ± 7.57</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>76.04 ± 9.71</t>
+          <t>76.02 ± 9.23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70.08 ± 13.21</t>
+          <t>69.81 ± 12.84</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>39.75 ± 15.85</t>
+          <t>40.08 ± 14.81</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>70.06 ± 13.23</t>
+          <t>69.75 ± 12.86</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>29.41 ± 7.53</t>
+          <t>29.13 ± 6.96</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>38.72 ± 23.23</t>
+          <t>37.41 ± 22.91</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>30.73 ± 22.07</t>
+          <t>30.03 ± 21.58</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -6062,52 +6062,52 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>69.78 ± 7.35</t>
+          <t>70.03 ± 7.36</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>71.03 ± 6.89</t>
+          <t>71.36 ± 6.90</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>70.79 ± 7.11</t>
+          <t>71.15 ± 7.05</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>76.51 ± 8.59</t>
+          <t>76.73 ± 8.66</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>68.92 ± 11.87</t>
+          <t>69.57 ± 11.69</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>39.05 ± 14.13</t>
+          <t>39.65 ± 14.18</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>68.88 ± 11.89</t>
+          <t>69.54 ± 11.72</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>30.24 ± 7.58</t>
+          <t>30.67 ± 7.86</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>40.51 ± 18.64</t>
+          <t>41.50 ± 18.49</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>31.54 ± 16.29</t>
+          <t>32.75 ± 15.99</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -6494,52 +6494,52 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>69.32 ± 8.01</t>
+          <t>69.08 ± 7.89</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>71.09 ± 6.34</t>
+          <t>70.78 ± 6.37</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70.77 ± 6.94</t>
+          <t>70.52 ± 6.89</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>77.07 ± 9.56</t>
+          <t>76.54 ± 9.61</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>66.05 ± 12.82</t>
+          <t>65.48 ± 12.56</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>37.81 ± 14.92</t>
+          <t>37.32 ± 14.76</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>66.01 ± 12.83</t>
+          <t>65.40 ± 12.57</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>29.60 ± 7.01</t>
+          <t>29.67 ± 6.85</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>38.13 ± 21.41</t>
+          <t>37.31 ± 21.60</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>29.79 ± 19.27</t>
+          <t>27.95 ± 18.43</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6926,52 +6926,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>68.47 ± 8.89</t>
+          <t>67.72 ± 9.61</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>72.18 ± 5.57</t>
+          <t>71.60 ± 6.43</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>71.81 ± 6.40</t>
+          <t>71.14 ± 7.33</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>78.57 ± 8.38</t>
+          <t>77.86 ± 9.03</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>61.62 ± 12.24</t>
+          <t>60.90 ± 13.55</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>35.33 ± 14.98</t>
+          <t>33.86 ± 16.84</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>61.61 ± 12.18</t>
+          <t>60.83 ± 13.57</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>28.24 ± 6.97</t>
+          <t>28.78 ± 6.81</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>37.19 ± 17.52</t>
+          <t>36.96 ± 19.34</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>27.17 ± 14.96</t>
+          <t>28.09 ± 17.09</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -7358,52 +7358,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>69.02 ± 11.83</t>
+          <t>67.18 ± 11.78</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>76.97 ± 8.69</t>
+          <t>75.40 ± 8.78</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>76.41 ± 8.84</t>
+          <t>74.81 ± 9.00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>78.35 ± 12.69</t>
+          <t>77.70 ± 12.27</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>58.69 ± 18.17</t>
+          <t>57.75 ± 17.33</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>38.67 ± 22.73</t>
+          <t>34.75 ± 22.52</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>58.58 ± 18.21</t>
+          <t>57.64 ± 17.37</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>26.98 ± 11.03</t>
+          <t>28.41 ± 11.04</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>43.35 ± 27.62</t>
+          <t>44.08 ± 27.23</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>32.12 ± 23.36</t>
+          <t>31.45 ± 22.14</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -7790,52 +7790,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>64.41 ± 13.71</t>
+          <t>65.48 ± 12.79</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>76.41 ± 8.76</t>
+          <t>76.90 ± 8.42</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>74.90 ± 9.95</t>
+          <t>75.66 ± 9.26</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>77.30 ± 11.15</t>
+          <t>77.12 ± 11.75</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>51.98 ± 19.03</t>
+          <t>52.72 ± 19.43</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>27.96 ± 26.36</t>
+          <t>30.42 ± 24.23</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>51.89 ± 19.04</t>
+          <t>52.62 ± 19.44</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>28.72 ± 8.36</t>
+          <t>28.65 ± 9.02</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>38.41 ± 29.09</t>
+          <t>37.63 ± 29.69</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>29.10 ± 25.59</t>
+          <t>31.60 ± 27.17</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -8222,52 +8222,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>65.09 ± 14.72</t>
+          <t>65.84 ± 14.09</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>79.89 ± 11.19</t>
+          <t>79.68 ± 11.51</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>79.68 ± 9.69</t>
+          <t>79.63 ± 10.05</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>80.01 ± 12.94</t>
+          <t>79.87 ± 12.83</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>52.88 ± 22.81</t>
+          <t>53.07 ± 22.57</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>32.68 ± 28.25</t>
+          <t>33.83 ± 27.95</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>52.72 ± 22.78</t>
+          <t>52.93 ± 22.54</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>27.01 ± 11.01</t>
+          <t>27.70 ± 11.60</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>45.52 ± 31.40</t>
+          <t>46.18 ± 30.91</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>36.23 ± 27.35</t>
+          <t>39.70 ± 28.77</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -8654,52 +8654,52 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>64.94 ± 14.16</t>
+          <t>64.49 ± 13.85</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>81.75 ± 9.27</t>
+          <t>81.65 ± 9.60</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>81.12 ± 8.43</t>
+          <t>81.05 ± 8.67</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>81.17 ± 11.29</t>
+          <t>81.26 ± 11.31</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>51.09 ± 22.56</t>
+          <t>51.14 ± 23.03</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>32.50 ± 27.76</t>
+          <t>32.28 ± 27.82</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>50.98 ± 22.56</t>
+          <t>51.03 ± 23.05</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>25.71 ± 9.11</t>
+          <t>25.08 ± 9.55</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>39.54 ± 29.97</t>
+          <t>38.59 ± 30.38</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>34.27 ± 28.71</t>
+          <t>34.29 ± 28.91</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -9086,52 +9086,52 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>59.63 ± 13.37</t>
+          <t>60.64 ± 13.95</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>80.69 ± 9.19</t>
+          <t>80.89 ± 9.23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>79.84 ± 8.36</t>
+          <t>80.16 ± 8.44</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>76.61 ± 13.11</t>
+          <t>77.16 ± 13.60</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>41.27 ± 23.52</t>
+          <t>42.55 ± 24.25</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>22.07 ± 27.81</t>
+          <t>23.60 ± 28.06</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>41.12 ± 23.53</t>
+          <t>42.38 ± 24.23</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>29.31 ± 10.72</t>
+          <t>28.21 ± 11.54</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>33.09 ± 30.85</t>
+          <t>33.37 ± 31.18</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>27.15 ± 27.21</t>
+          <t>28.93 ± 29.34</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -9518,52 +9518,52 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>58.80 ± 13.22</t>
+          <t>58.66 ± 13.99</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>81.03 ± 8.17</t>
+          <t>80.89 ± 8.86</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>79.91 ± 8.13</t>
+          <t>79.84 ± 8.68</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>74.96 ± 9.07</t>
+          <t>74.77 ± 8.77</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>32.54 ± 20.47</t>
+          <t>31.90 ± 19.69</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>11.81 ± 18.38</t>
+          <t>11.78 ± 20.33</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>37.38 ± 17.87</t>
+          <t>36.68 ± 17.11</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>38.68 ± 21.48</t>
+          <t>38.84 ± 21.37</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>27.16 ± 24.13</t>
+          <t>26.18 ± 22.27</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>20.53 ± 21.83</t>
+          <t>18.97 ± 19.27</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
